--- a/r5-core-76-add-healthcare-service/ValueSet-at-funktionscode-vs.xlsx
+++ b/r5-core-76-add-healthcare-service/ValueSet-at-funktionscode-vs.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ATFunktionscodeVS</t>
+    <t>HealthcareServiceSpecialtyVS</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T21:36:48+00:00</t>
+    <t>2026-10-11T20:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/core/r5/CodeSystem/at-funktionscode</t>
+    <t>https://fhir.hl7.at/core/r5/CodeSystem/at-core-funktionscode</t>
   </si>
 </sst>
 </file>

--- a/r5-core-76-add-healthcare-service/ValueSet-at-funktionscode-vs.xlsx
+++ b/r5-core-76-add-healthcare-service/ValueSet-at-funktionscode-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T20:03:30+00:00</t>
+    <t>2026-10-12T11:43:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
